--- a/data/A1_vocab.xlsx
+++ b/data/A1_vocab.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12285" activeTab="5"/>
+    <workbookView windowWidth="28800" windowHeight="12285" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Day 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="791">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="830">
   <si>
     <t>german_word</t>
   </si>
@@ -1729,13 +1729,19 @@
     <t>Ich koche Suppe.</t>
   </si>
   <si>
+    <t>to bake</t>
+  </si>
+  <si>
+    <t>to eat</t>
+  </si>
+  <si>
     <t>verb</t>
   </si>
   <si>
     <t>🍲</t>
   </si>
   <si>
-    <t>cooking chef stove pot kitchen</t>
+    <t>cooking chef stove pot soup kitchen</t>
   </si>
   <si>
     <t>Verb</t>
@@ -1750,10 +1756,19 @@
     <t>Ich mache Hausaufgaben.</t>
   </si>
   <si>
+    <t>to write</t>
+  </si>
+  <si>
+    <t>to build</t>
+  </si>
+  <si>
+    <t>to read</t>
+  </si>
+  <si>
     <t>✍️</t>
   </si>
   <si>
-    <t>doing homework writing</t>
+    <t>doing homework notebook pencil work</t>
   </si>
   <si>
     <t>suchen</t>
@@ -1765,10 +1780,16 @@
     <t>Ich suche mein Buch.</t>
   </si>
   <si>
+    <t>to find</t>
+  </si>
+  <si>
+    <t>to watch</t>
+  </si>
+  <si>
     <t>📖</t>
   </si>
   <si>
-    <t>searching magnifying glass map</t>
+    <t>searching magnifying glass lost book library</t>
   </si>
   <si>
     <t>trinken</t>
@@ -1780,10 +1801,13 @@
     <t>Ich trinke Wasser.</t>
   </si>
   <si>
+    <t>to sleep</t>
+  </si>
+  <si>
     <t>💧</t>
   </si>
   <si>
-    <t>drinking glass water sip</t>
+    <t>drinking water glass bottle hydration</t>
   </si>
   <si>
     <t>hören</t>
@@ -1795,10 +1819,16 @@
     <t>Ich höre Musik.</t>
   </si>
   <si>
+    <t>to see</t>
+  </si>
+  <si>
+    <t>to speak</t>
+  </si>
+  <si>
     <t>🎧</t>
   </si>
   <si>
-    <t>headphones listening music girl</t>
+    <t>headphones listening music audio sound</t>
   </si>
   <si>
     <t>fragen</t>
@@ -1810,10 +1840,19 @@
     <t>Ich frage den Lehrer.</t>
   </si>
   <si>
+    <t>to answer</t>
+  </si>
+  <si>
+    <t>to tell</t>
+  </si>
+  <si>
+    <t>to listen</t>
+  </si>
+  <si>
     <t>🙋‍♂️</t>
   </si>
   <si>
-    <t>raising hand classroom pupil</t>
+    <t>raising hand classroom question student teacher</t>
   </si>
   <si>
     <t>lieben</t>
@@ -1825,10 +1864,19 @@
     <t>Ich liebe meine Familie.</t>
   </si>
   <si>
+    <t>to like</t>
+  </si>
+  <si>
+    <t>to hate</t>
+  </si>
+  <si>
+    <t>to help</t>
+  </si>
+  <si>
     <t>❤️</t>
   </si>
   <si>
-    <t>heart love couples</t>
+    <t>heart family love affection care</t>
   </si>
   <si>
     <t>trinken (Wasser)</t>
@@ -1840,7 +1888,16 @@
     <t>Ich trinke viel Wasser.</t>
   </si>
   <si>
-    <t>drinking clean glass water</t>
+    <t>to buy water</t>
+  </si>
+  <si>
+    <t>to boil water</t>
+  </si>
+  <si>
+    <t>to find water</t>
+  </si>
+  <si>
+    <t>drinking clean water glass hydration healthy</t>
   </si>
   <si>
     <t>trinken (Bier)</t>
@@ -1852,10 +1909,19 @@
     <t>Er trinkt gern Bier.</t>
   </si>
   <si>
+    <t>to buy beer</t>
+  </si>
+  <si>
+    <t>to sell beer</t>
+  </si>
+  <si>
+    <t>to brew beer</t>
+  </si>
+  <si>
     <t>🍺</t>
   </si>
   <si>
-    <t>german beer stein tankard pint</t>
+    <t>german beer mug stein pub drink alcohol</t>
   </si>
   <si>
     <t>Wie spät ist es?</t>
@@ -1867,10 +1933,19 @@
     <t>Wie spät ist es jetzt?</t>
   </si>
   <si>
+    <t>What is your name?</t>
+  </si>
+  <si>
+    <t>Where do you live?</t>
+  </si>
+  <si>
+    <t>How are you?</t>
+  </si>
+  <si>
     <t>🕒</t>
   </si>
   <si>
-    <t>antique wall clock</t>
+    <t>wall clock time question clock face analog</t>
   </si>
   <si>
     <t>Wie viel Uhr ist es?</t>
@@ -1882,7 +1957,13 @@
     <t>Wie viel Uhr ist es bitte?</t>
   </si>
   <si>
-    <t>elegant wrist watch design</t>
+    <t>What day is today?</t>
+  </si>
+  <si>
+    <t>When are you coming?</t>
+  </si>
+  <si>
+    <t>wrist watch clock time asking digital analog</t>
   </si>
   <si>
     <t>Uhr</t>
@@ -1891,13 +1972,19 @@
     <t>Es ist drei Uhr.</t>
   </si>
   <si>
+    <t>Calendar</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
     <t>time</t>
   </si>
   <si>
     <t>🕰️</t>
   </si>
   <si>
-    <t>clock dials hands</t>
+    <t>clock dial wall clock hands timepiece</t>
   </si>
   <si>
     <t>Time Component</t>
@@ -1912,10 +1999,19 @@
     <t>Es dauert fünf Minuten.</t>
   </si>
   <si>
+    <t>Second</t>
+  </si>
+  <si>
+    <t>Hour</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
     <t>⏳</t>
   </si>
   <si>
-    <t>minute sand stopwatch hourglass</t>
+    <t>stopwatch timer minute hand countdown clock</t>
   </si>
   <si>
     <t>Vor</t>
@@ -1927,7 +2023,13 @@
     <t>Es ist zehn vor drei.</t>
   </si>
   <si>
-    <t>back arrow reverse navigation</t>
+    <t>Since</t>
+  </si>
+  <si>
+    <t>Until</t>
+  </si>
+  <si>
+    <t>clock before hour backward arrow time direction</t>
   </si>
   <si>
     <t>Nach</t>
@@ -1939,7 +2041,7 @@
     <t>Es ist fünf nach zwei.</t>
   </si>
   <si>
-    <t>forward arrow next icon</t>
+    <t>clock after hour forward arrow time direction</t>
   </si>
   <si>
     <t>Viertel nach</t>
@@ -1951,7 +2053,16 @@
     <t>Es ist Viertel nach eins.</t>
   </si>
   <si>
-    <t>clock quarter past three</t>
+    <t>Half past</t>
+  </si>
+  <si>
+    <t>Quarter to</t>
+  </si>
+  <si>
+    <t>Full hour</t>
+  </si>
+  <si>
+    <t>quarter past clock 15 minutes analog clock</t>
   </si>
   <si>
     <t>Halb</t>
@@ -1963,10 +2074,13 @@
     <t>Es ist halb drei.</t>
   </si>
   <si>
+    <t>Quarter past</t>
+  </si>
+  <si>
     <t>🌓</t>
   </si>
   <si>
-    <t>moon phase half slice crescent</t>
+    <t>half past clock 30 minutes time learning</t>
   </si>
   <si>
     <t>Viertel vor</t>
@@ -1978,7 +2092,7 @@
     <t>Es ist Viertel vor vier.</t>
   </si>
   <si>
-    <t>clock quarter to nine hourglass</t>
+    <t>quarter to clock countdown time learning</t>
   </si>
   <si>
     <t>Dreiviertel</t>
@@ -1990,10 +2104,13 @@
     <t>Es ist Dreiviertel zwölf.</t>
   </si>
   <si>
+    <t>30 Minutes Past</t>
+  </si>
+  <si>
     <t>🥧</t>
   </si>
   <si>
-    <t>pie chart three quarters diagram</t>
+    <t>three quarters clock 45 minutes pie chart time</t>
   </si>
   <si>
     <t>langsam</t>
@@ -2400,12 +2517,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2419,13 +2536,6 @@
       <color rgb="FFE2E8F0"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
@@ -2443,7 +2553,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2451,17 +2561,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2479,22 +2589,24 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2524,16 +2636,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2547,21 +2673,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="15"/>
       <color theme="3"/>
@@ -2570,11 +2681,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2593,7 +2703,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2605,19 +2727,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2635,30 +2745,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2671,7 +2757,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2683,7 +2865,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2695,85 +2877,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2802,67 +2912,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2885,8 +2939,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2895,155 +2964,196 @@
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3052,12 +3162,12 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3422,800 +3532,800 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" ht="18" spans="1:12">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:12">
+      <c r="A7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:12">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:12">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="L19" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:12">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="L20" s="4" t="s">
+      <c r="L20" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K21" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="L21" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4243,990 +4353,990 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:12">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="L19" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="L20" s="4" t="s">
+      <c r="L20" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:12">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K21" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="L21" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L22" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:12">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J24" s="4" t="s">
+      <c r="J24" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="K24" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="L24" s="4" t="s">
+      <c r="L24" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="K25" s="4" t="s">
+      <c r="K25" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="L25" s="4" t="s">
+      <c r="L25" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J26" s="4" t="s">
+      <c r="J26" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="K26" s="4" t="s">
+      <c r="K26" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="L26" s="4" t="s">
+      <c r="L26" s="3" t="s">
         <v>183</v>
       </c>
     </row>
@@ -5257,762 +5367,762 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:12">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:12">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:12">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:12">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:12">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:12">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="L19" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="L20" s="4" t="s">
+      <c r="L20" s="3" t="s">
         <v>22</v>
       </c>
     </row>
@@ -6042,1104 +6152,1104 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="L4" s="4" t="s">
+      <c r="L4" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:12">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="L6" s="4" t="s">
+      <c r="L6" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="L7" s="4" t="s">
+      <c r="L7" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="L8" s="4" t="s">
+      <c r="L8" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="L9" s="4" t="s">
+      <c r="L9" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="L10" s="4" t="s">
+      <c r="L10" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:12">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="L11" s="4" t="s">
+      <c r="L11" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="L12" s="4" t="s">
+      <c r="L12" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:12">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="L13" s="4" t="s">
+      <c r="L13" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K14" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="L14" s="4" t="s">
+      <c r="L14" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:12">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K15" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="L15" s="4" t="s">
+      <c r="L15" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J16" s="4" t="s">
+      <c r="J16" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K16" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="L16" s="4" t="s">
+      <c r="L16" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:12">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J17" s="4" t="s">
+      <c r="J17" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K17" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="L17" s="4" t="s">
+      <c r="L17" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J18" s="4" t="s">
+      <c r="J18" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K18" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="L18" s="4" t="s">
+      <c r="L18" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:12">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J19" s="4" t="s">
+      <c r="J19" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="K19" s="4" t="s">
+      <c r="K19" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="L19" s="4" t="s">
+      <c r="L19" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K20" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="L20" s="4" t="s">
+      <c r="L20" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:12">
-      <c r="A21" s="4" t="s">
+      <c r="A21" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J21" s="4" t="s">
+      <c r="J21" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="K21" s="4" t="s">
+      <c r="K21" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="L21" s="4" t="s">
+      <c r="L21" s="3" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:12">
-      <c r="A22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J22" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K22" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L22" s="3" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="23" spans="1:12">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="J23" s="4" t="s">
+      <c r="J23" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="K23" s="4" t="s">
+      <c r="K23" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="L23" s="4" t="s">
+      <c r="L23" s="3" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="24" spans="1:12">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="J24" s="4" t="s">
+      <c r="J24" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="K24" s="4" t="s">
+      <c r="K24" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="L24" s="4" t="s">
+      <c r="L24" s="3" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="25" spans="1:12">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="H25" s="4" t="s">
+      <c r="H25" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="I25" s="4" t="s">
+      <c r="I25" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="J25" s="4" t="s">
+      <c r="J25" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="K25" s="4" t="s">
+      <c r="K25" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="L25" s="4" t="s">
+      <c r="L25" s="3" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="26" spans="1:12">
-      <c r="A26" s="4" t="s">
+      <c r="A26" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H26" s="4" t="s">
+      <c r="H26" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="I26" s="4" t="s">
+      <c r="I26" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="J26" s="4" t="s">
+      <c r="J26" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="K26" s="4" t="s">
+      <c r="K26" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="L26" s="4" t="s">
+      <c r="L26" s="3" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="27" spans="1:12">
-      <c r="A27" s="4" t="s">
+      <c r="A27" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="J27" s="4" t="s">
+      <c r="J27" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="K27" s="4" t="s">
+      <c r="K27" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="L27" s="4" t="s">
+      <c r="L27" s="3" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="28" spans="1:12">
-      <c r="A28" s="4" t="s">
+      <c r="A28" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="J28" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="K28" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="L28" s="4" t="s">
+      <c r="L28" s="3" t="s">
         <v>535</v>
       </c>
     </row>
     <row r="29" spans="1:12">
-      <c r="A29" s="4" t="s">
+      <c r="A29" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="J29" s="4" t="s">
+      <c r="J29" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="K29" s="4" t="s">
+      <c r="K29" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="L29" s="4" t="s">
+      <c r="L29" s="3" t="s">
         <v>535</v>
       </c>
     </row>
@@ -7170,763 +7280,763 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>568</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>375</v>
+        <v>569</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>79</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>280</v>
+        <v>570</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="J2" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="E5" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="F5" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="L2" s="4" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="J5" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>331</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>580</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>221</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>582</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>585</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>587</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>572</v>
-      </c>
     </row>
     <row r="6" ht="18" spans="1:12">
-      <c r="A6" s="4" t="s">
-        <v>588</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="C6" s="4" t="s">
+      <c r="A6" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>590</v>
+      <c r="D6" s="3" t="s">
+        <v>598</v>
       </c>
       <c r="E6" s="4" t="s">
+        <v>599</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="H6" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>572</v>
+        <v>600</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:12">
-      <c r="A7" s="4" t="s">
-        <v>593</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>594</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="A7" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>595</v>
+      <c r="D7" s="3" t="s">
+        <v>605</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>392</v>
+        <v>606</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>47</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>250</v>
+        <v>607</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>572</v>
+        <v>608</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="A8" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>600</v>
+      <c r="D8" s="3" t="s">
+        <v>613</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>274</v>
+        <v>614</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>128</v>
+        <v>615</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>202</v>
+        <v>616</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="I8" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>601</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>572</v>
+      <c r="I8" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="9" spans="1:12">
-      <c r="A9" s="4" t="s">
-        <v>603</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>604</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="A9" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>605</v>
+      <c r="D9" s="3" t="s">
+        <v>621</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>56</v>
+        <v>622</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>18</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>227</v>
+        <v>623</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>572</v>
+        <v>624</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="10" spans="1:12">
-      <c r="A10" s="4" t="s">
-        <v>607</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="A10" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>609</v>
+      <c r="D10" s="3" t="s">
+        <v>628</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>122</v>
+        <v>629</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>274</v>
+        <v>630</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>128</v>
+        <v>631</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="I10" s="4" t="s">
-        <v>569</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>611</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>572</v>
+      <c r="I10" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>574</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:12">
-      <c r="A11" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>613</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="A11" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>614</v>
+      <c r="D11" s="3" t="s">
+        <v>636</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>178</v>
+        <v>637</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>153</v>
+        <v>638</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>245</v>
+        <v>639</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="L11" s="4" t="s">
+      <c r="J11" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="4" t="s">
-        <v>617</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="A12" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>619</v>
+      <c r="D12" s="3" t="s">
+        <v>644</v>
       </c>
       <c r="E12" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>509</v>
       </c>
-      <c r="F12" s="4" t="s">
-        <v>158</v>
-      </c>
       <c r="G12" s="4" t="s">
-        <v>300</v>
+        <v>645</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>620</v>
-      </c>
-      <c r="L12" s="4" t="s">
+      <c r="K12" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:12">
-      <c r="A13" s="4" t="s">
-        <v>621</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>622</v>
+      <c r="D13" s="3" t="s">
+        <v>649</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>221</v>
-      </c>
       <c r="G13" s="4" t="s">
-        <v>106</v>
+        <v>650</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>624</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>625</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>626</v>
+        <v>651</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:12">
-      <c r="A14" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>628</v>
-      </c>
-      <c r="C14" s="4" t="s">
+      <c r="A14" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>629</v>
+      <c r="D14" s="3" t="s">
+        <v>658</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>56</v>
+        <v>659</v>
       </c>
       <c r="F14" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>128</v>
-      </c>
       <c r="H14" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>338</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>631</v>
-      </c>
-      <c r="L14" s="4" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12">
-      <c r="A15" s="4" t="s">
-        <v>632</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>634</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>269</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>89</v>
+        <v>667</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J15" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="K15" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>626</v>
+      <c r="K15" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="16" spans="1:12">
-      <c r="A16" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>637</v>
-      </c>
-      <c r="C16" s="4" t="s">
+      <c r="A16" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>638</v>
+      <c r="D16" s="3" t="s">
+        <v>672</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>114</v>
-      </c>
       <c r="G16" s="4" t="s">
-        <v>14</v>
+        <v>668</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J16" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>626</v>
+      <c r="K16" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:12">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>641</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>615</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>643</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>626</v>
+      <c r="K17" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="18" spans="1:12">
-      <c r="A18" s="4" t="s">
-        <v>644</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="A18" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D18" s="4" t="s">
-        <v>646</v>
+      <c r="D18" s="3" t="s">
+        <v>683</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>72</v>
+        <v>684</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>160</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>86</v>
+        <v>678</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>648</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>626</v>
+        <v>679</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:12">
-      <c r="A19" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>650</v>
-      </c>
-      <c r="C19" s="4" t="s">
+      <c r="A19" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>651</v>
+      <c r="D19" s="3" t="s">
+        <v>689</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>357</v>
+        <v>677</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>123</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>350</v>
+        <v>684</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="K19" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="I19" s="3" t="s">
         <v>652</v>
       </c>
-      <c r="L19" s="4" t="s">
-        <v>626</v>
+      <c r="J19" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="20" spans="1:12">
-      <c r="A20" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>654</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="A20" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="D20" s="4" t="s">
-        <v>655</v>
+      <c r="D20" s="3" t="s">
+        <v>693</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>283</v>
+        <v>123</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>221</v>
+        <v>694</v>
       </c>
       <c r="G20" s="4" t="s">
         <v>509</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>656</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>657</v>
-      </c>
-      <c r="L20" s="4" t="s">
-        <v>626</v>
+        <v>283</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>655</v>
       </c>
     </row>
   </sheetData>
@@ -7981,596 +8091,596 @@
     </row>
     <row r="2" spans="1:12">
       <c r="A2" s="2" t="s">
-        <v>658</v>
+        <v>697</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>659</v>
+        <v>698</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>660</v>
+        <v>699</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>661</v>
+        <v>700</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>660</v>
+        <v>699</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>662</v>
+        <v>701</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>663</v>
+        <v>702</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>664</v>
+        <v>703</v>
       </c>
       <c r="I2" s="2"/>
       <c r="J2" s="2" t="s">
-        <v>665</v>
+        <v>704</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>666</v>
+        <v>705</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>667</v>
+        <v>706</v>
       </c>
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>668</v>
+        <v>707</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>669</v>
+        <v>708</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>662</v>
+        <v>701</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>670</v>
+        <v>709</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>662</v>
+        <v>701</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>660</v>
+        <v>699</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>671</v>
+        <v>710</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>672</v>
+        <v>711</v>
       </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
         <v>253</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>673</v>
+        <v>712</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>667</v>
+        <v>706</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2" t="s">
-        <v>674</v>
+        <v>713</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>675</v>
+        <v>714</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>676</v>
+        <v>715</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>677</v>
+        <v>716</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>678</v>
+        <v>717</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>679</v>
+        <v>718</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>680</v>
+        <v>719</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>681</v>
+        <v>720</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>682</v>
+        <v>721</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>683</v>
+        <v>722</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>684</v>
+        <v>723</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="2" t="s">
-        <v>686</v>
+        <v>725</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>687</v>
+        <v>726</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>688</v>
+        <v>727</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>689</v>
+        <v>728</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>690</v>
+        <v>729</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>691</v>
+        <v>730</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>692</v>
+        <v>731</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>693</v>
+        <v>732</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>694</v>
+        <v>733</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>400</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>690</v>
+        <v>729</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" s="2" t="s">
-        <v>695</v>
+        <v>734</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>735</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>697</v>
+        <v>736</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>698</v>
+        <v>737</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>697</v>
+        <v>736</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>699</v>
+        <v>738</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>700</v>
+        <v>739</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>701</v>
+        <v>740</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>682</v>
+        <v>721</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>370</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>697</v>
+        <v>736</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" s="2" t="s">
-        <v>702</v>
+        <v>741</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>703</v>
+        <v>742</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>704</v>
+        <v>743</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>705</v>
+        <v>744</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>704</v>
+        <v>743</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>706</v>
+        <v>745</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>707</v>
+        <v>746</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>708</v>
+        <v>747</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>682</v>
+        <v>721</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>709</v>
+        <v>748</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>704</v>
+        <v>743</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>710</v>
+        <v>749</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>711</v>
+        <v>750</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>712</v>
+        <v>751</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>713</v>
+        <v>752</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>714</v>
+        <v>753</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>715</v>
+        <v>754</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>716</v>
+        <v>755</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>700</v>
+        <v>739</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>692</v>
+        <v>731</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>682</v>
+        <v>721</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>115</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>715</v>
+        <v>754</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" s="2" t="s">
-        <v>717</v>
+        <v>756</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>718</v>
+        <v>757</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>719</v>
+        <v>758</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>720</v>
+        <v>759</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>719</v>
+        <v>758</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>721</v>
+        <v>760</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>722</v>
+        <v>761</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>723</v>
+        <v>762</v>
       </c>
       <c r="I9" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="L9" s="2" t="s">
         <v>724</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="2" t="s">
-        <v>726</v>
+        <v>765</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>727</v>
+        <v>766</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>159</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>728</v>
+        <v>767</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>729</v>
+        <v>768</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>730</v>
+        <v>769</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>731</v>
+        <v>770</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2" t="s">
         <v>161</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>732</v>
+        <v>771</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>667</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>778</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>733</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>736</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>735</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>737</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>739</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>258</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>735</v>
+        <v>774</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" s="2" t="s">
-        <v>740</v>
+        <v>779</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>741</v>
+        <v>780</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>742</v>
+        <v>781</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>743</v>
+        <v>782</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>744</v>
+        <v>783</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>745</v>
+        <v>784</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>746</v>
+        <v>785</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>747</v>
+        <v>786</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2" t="s">
-        <v>748</v>
+        <v>787</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>749</v>
+        <v>788</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="2" t="s">
-        <v>750</v>
+        <v>789</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>751</v>
+        <v>790</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>753</v>
+        <v>792</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>754</v>
+        <v>793</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>755</v>
+        <v>794</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>756</v>
+        <v>795</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>694</v>
+        <v>733</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>757</v>
+        <v>796</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>752</v>
+        <v>791</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>685</v>
+        <v>724</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" s="2" t="s">
-        <v>758</v>
+        <v>797</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>759</v>
+        <v>798</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>716</v>
+        <v>755</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>760</v>
+        <v>799</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>716</v>
+        <v>755</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>761</v>
+        <v>800</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>692</v>
+        <v>731</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>762</v>
+        <v>801</v>
       </c>
       <c r="I14" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>803</v>
+      </c>
+      <c r="L14" s="2" t="s">
         <v>724</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>685</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" s="2" t="s">
-        <v>765</v>
+        <v>804</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>766</v>
+        <v>805</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>767</v>
+        <v>806</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>768</v>
+        <v>807</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>769</v>
+        <v>808</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>770</v>
+        <v>809</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>744</v>
+        <v>783</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>745</v>
+        <v>784</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2" t="s">
-        <v>771</v>
+        <v>810</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>772</v>
+        <v>811</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" s="2" t="s">
-        <v>773</v>
+        <v>812</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>774</v>
+        <v>813</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>775</v>
+        <v>814</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>776</v>
+        <v>815</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>777</v>
+        <v>816</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>778</v>
+        <v>817</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>779</v>
+        <v>818</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>780</v>
+        <v>819</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2" t="s">
         <v>190</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>781</v>
+        <v>820</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="2" t="s">
-        <v>782</v>
+        <v>821</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>783</v>
+        <v>822</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>784</v>
+        <v>823</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>785</v>
+        <v>824</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>784</v>
+        <v>823</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>786</v>
+        <v>825</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>787</v>
+        <v>826</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>788</v>
+        <v>827</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2" t="s">
         <v>216</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>789</v>
+        <v>828</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>790</v>
+        <v>829</v>
       </c>
     </row>
   </sheetData>

--- a/data/A1_vocab.xlsx
+++ b/data/A1_vocab.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12285" activeTab="8"/>
+    <workbookView windowWidth="28800" windowHeight="12285"/>
   </bookViews>
   <sheets>
     <sheet name="Day 1" sheetId="1" r:id="rId1"/>
@@ -4083,10 +4083,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -4157,6 +4157,29 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
@@ -4164,11 +4187,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4180,17 +4202,34 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -4202,32 +4241,31 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4242,44 +4280,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -4306,6 +4306,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -4318,7 +4324,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4330,7 +4336,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4342,7 +4360,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4354,7 +4378,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4366,37 +4456,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4408,73 +4468,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4509,6 +4509,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -4524,11 +4533,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4544,30 +4568,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4601,8 +4601,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -4612,136 +4612,136 @@
     <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
